--- a/Assignments/Schedule_Ass1_Adv_ML.xlsx
+++ b/Assignments/Schedule_Ass1_Adv_ML.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thibaut/Documents/DTU/Advanced ML/Advanced_ML_GitHub/Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81598C90-4415-5143-A80A-9B6EA850A193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ABD32F-9E92-1740-8FC1-271C41326F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="26740" windowHeight="15160" xr2:uid="{2A1B1279-A485-004F-A728-48BBE980049D}"/>
+    <workbookView xWindow="60" yWindow="760" windowWidth="26740" windowHeight="15160" xr2:uid="{2A1B1279-A485-004F-A728-48BBE980049D}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
   <si>
     <t>SCHEDULE ADLCV WEEK 2</t>
   </si>
@@ -53,12 +53,6 @@
     <t>Command</t>
   </si>
   <si>
-    <t>Test accuracy</t>
-  </si>
-  <si>
-    <t>Test loss</t>
-  </si>
-  <si>
     <t>Lat-dim</t>
   </si>
   <si>
@@ -93,6 +87,15 @@
   </si>
   <si>
     <t>Flow</t>
+  </si>
+  <si>
+    <t>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py</t>
+  </si>
+  <si>
+    <t>ELBO Loss</t>
+  </si>
+  <si>
+    <t>Test Likelihood</t>
   </si>
 </sst>
 </file>
@@ -612,7 +615,8 @@
   <cols>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="45.33203125" customWidth="1"/>
     <col min="11" max="11" width="174.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="53.5" bestFit="1" customWidth="1"/>
@@ -637,28 +641,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>3</v>
@@ -667,7 +671,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -675,10 +679,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="14">
         <v>32</v>
@@ -690,7 +694,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2">
         <v>0.78100000000000003</v>
@@ -707,7 +711,7 @@
         <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  01_bs32_ep20_lat-dim20_priorStandard.pt</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -716,10 +720,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="14">
         <v>32</v>
@@ -731,7 +735,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H4" s="3">
         <v>0.8</v>
@@ -754,10 +758,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="14">
         <v>32</v>
@@ -769,7 +773,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3">
         <v>0.80400000000000005</v>
@@ -792,10 +796,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="14">
         <v>32</v>
@@ -807,7 +811,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" s="3">
         <v>0.79100000000000004</v>
@@ -830,10 +834,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" s="14">
         <v>32</v>
@@ -845,7 +849,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3">
         <v>0.54200000000000004</v>
@@ -855,11 +859,14 @@
       </c>
       <c r="J7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>05_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>05_bs32_ep20_lat-dim20_priorFlow.pt</v>
       </c>
       <c r="K7" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  05_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Flow --model  05_bs32_ep20_lat-dim20_priorFlow.pt</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -868,10 +875,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" s="14">
         <v>32</v>
@@ -883,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="3">
         <v>0.78500000000000003</v>
@@ -893,11 +900,11 @@
       </c>
       <c r="J8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>06_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>06_bs32_ep20_lat-dim20_priorGM.pt</v>
       </c>
       <c r="K8" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  06_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior GM --model  06_bs32_ep20_lat-dim20_priorGM.pt</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -906,10 +913,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" s="14">
         <v>32</v>
@@ -921,7 +928,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H9" s="3">
         <v>0.80700000000000005</v>
@@ -944,10 +951,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" s="14">
         <v>32</v>
@@ -959,7 +966,7 @@
         <v>20</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3">
         <v>0.80300000000000005</v>
@@ -969,11 +976,11 @@
       </c>
       <c r="J10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>08_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>08_bs32_ep20_lat-dim20_priorFlow.pt</v>
       </c>
       <c r="K10" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  08_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Flow --model  08_bs32_ep20_lat-dim20_priorFlow.pt</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -982,10 +989,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="14">
         <v>32</v>
@@ -997,7 +1004,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="3">
         <v>0.80200000000000005</v>
@@ -1007,11 +1014,11 @@
       </c>
       <c r="J11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>09_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>09_bs32_ep20_lat-dim20_priorGM.pt</v>
       </c>
       <c r="K11" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  09_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior GM --model  09_bs32_ep20_lat-dim20_priorGM.pt</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1020,10 +1027,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" s="14">
         <v>32</v>
@@ -1035,7 +1042,7 @@
         <v>20</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H12" s="3">
         <v>0.78700000000000003</v>
@@ -1058,10 +1065,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="14">
         <v>32</v>
@@ -1073,7 +1080,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3">
         <v>0.74399999999999999</v>
@@ -1083,11 +1090,11 @@
       </c>
       <c r="J13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>011_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>011_bs32_ep20_lat-dim20_priorFlow.pt</v>
       </c>
       <c r="K13" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  011_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Flow --model  011_bs32_ep20_lat-dim20_priorFlow.pt</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1096,10 +1103,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="14">
         <v>32</v>
@@ -1111,7 +1118,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="3">
         <v>0.80500000000000005</v>
@@ -1121,11 +1128,11 @@
       </c>
       <c r="J14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>012_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>012_bs32_ep20_lat-dim20_priorGM.pt</v>
       </c>
       <c r="K14" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior Standard --model  012_bs32_ep20_lat-dim20_priorStandard.pt</v>
+        <v>python3 Advanced_ML_GitHub/Exercises/Week_2/vae_bernoulli_flow.py train --device mps --batch-size 32 --epochs 20 --latent-dim 20 --prior GM --model  012_bs32_ep20_lat-dim20_priorGM.pt</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -1134,10 +1141,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="14">
         <v>32</v>
@@ -1149,7 +1156,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3">
         <v>0.82899999999999996</v>
